--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104750_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104750_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8363</v>
+        <v>4.0352</v>
       </c>
       <c r="E2" t="n">
-        <v>9.238300000000001</v>
+        <v>6.751</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4021</v>
+        <v>-2.7157</v>
       </c>
       <c r="G2" t="n">
         <v>-1.927</v>
@@ -610,13 +610,13 @@
         <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3664</v>
+        <v>1.5654</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5529</v>
+        <v>1.0655</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8135</v>
+        <v>0.4999</v>
       </c>
       <c r="V2" t="n">
         <v>3.4863</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0318</v>
+        <v>1.7842</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6226</v>
+        <v>6.0964</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.5908</v>
+        <v>-4.3123</v>
       </c>
       <c r="G3" t="n">
         <v>3.244</v>
@@ -688,13 +688,13 @@
         <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3326</v>
+        <v>0.0849</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2547</v>
+        <v>-0.7809</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5872</v>
+        <v>0.8658</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0895</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4264</v>
+        <v>1.4891</v>
       </c>
       <c r="E4" t="n">
         <v>1.0687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3577</v>
+        <v>0.4204</v>
       </c>
       <c r="G4" t="n">
         <v>1.3845</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0418</v>
+        <v>0.1046</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0418</v>
+        <v>0.1046</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0847</v>
+        <v>0.3292</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4639</v>
+        <v>2.1136</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3792</v>
+        <v>-1.7844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3427</v>
+        <v>1.2622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3992</v>
+        <v>0.8656</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0565</v>
+        <v>0.3967</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5861</v>
+        <v>3.3787</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5861</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.3832</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2433</v>
+        <v>-2.1164</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1868</v>
+        <v>-0.13</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0565</v>
+        <v>-1.9865</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2276</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2276</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6038</v>
+        <v>-0.4681</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8779</v>
+        <v>0.0112</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.274</v>
+        <v>-0.4793</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0895</v>
+        <v>0.2179</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0895</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7195</v>
+        <v>-0.3263</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2844</v>
+        <v>0.9901</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.004</v>
+        <v>-1.3165</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2622</v>
+        <v>0.3427</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8656</v>
+        <v>0.3992</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3967</v>
+        <v>-0.0565</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3787</v>
+        <v>0.5861</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3832</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1164</v>
+        <v>-0.2433</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.13</v>
+        <v>-0.1868</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9865</v>
+        <v>-0.0565</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6829</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8211</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1382</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5167</v>
+        <v>0.1928</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8179</v>
+        <v>0.4041</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6988</v>
+        <v>-0.2113</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2179</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3268</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6386</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1132</v>
+        <v>2.4271</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5254</v>
+        <v>-3.226</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6026</v>
+        <v>1.0757</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2641</v>
+        <v>1.1977</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8667</v>
+        <v>-0.122</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3038</v>
+        <v>3.4239</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1549</v>
+        <v>2.62</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1489</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9064</v>
+        <v>-2.3481</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8907</v>
+        <v>-1.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0157</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6829</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1382</v>
+        <v>-1.5934</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4553</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3531</v>
+        <v>-0.2323</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2788</v>
+        <v>0.5966</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0743</v>
+        <v>-0.8289</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1871</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1871</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8022</v>
+        <v>-1.1578</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3611</v>
+        <v>0.2422</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1632</v>
+        <v>-1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0757</v>
+        <v>-0.6026</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1977</v>
+        <v>0.2641</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.122</v>
+        <v>-0.8667</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4239</v>
+        <v>1.3038</v>
       </c>
       <c r="K9" t="n">
-        <v>2.62</v>
+        <v>1.1549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.1489</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3481</v>
+        <v>-1.9064</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4223</v>
+        <v>-0.8907</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-1.0157</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4553</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5934</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1382</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2355</v>
+        <v>0.1277</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4694</v>
+        <v>0.0765</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7661</v>
+        <v>0.0512</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1871</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5615</v>
+        <v>-4.1411</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.083</v>
+        <v>0.0985</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4785</v>
+        <v>-4.2396</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.1519</v>
+        <v>1.8222</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4563</v>
+        <v>1.9506</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.6956</v>
+        <v>-0.1284</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.7732</v>
+        <v>4.6005</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8381</v>
+        <v>2.7989</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.9351</v>
+        <v>1.8016</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3786</v>
+        <v>-2.7783</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6182</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7604</v>
+        <v>-1.93</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1382</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.0974</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1382</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3839</v>
+        <v>-0.2706</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5325</v>
+        <v>-0.4046</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1486</v>
+        <v>0.1339</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9317</v>
+        <v>-2.5058</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0895</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9459</v>
+        <v>-5.1619</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6121</v>
+        <v>-2.8568</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3337</v>
+        <v>-2.3051</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8222</v>
+        <v>-4.2869</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9506</v>
+        <v>-2.1169</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1284</v>
+        <v>-2.17</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6005</v>
+        <v>-2.227</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7989</v>
+        <v>-1.3552</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8016</v>
+        <v>-0.8718</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7783</v>
+        <v>-2.0599</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.7617</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.93</v>
+        <v>-1.2982</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.1868</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.0974</v>
+        <v>-0.6829</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9105</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0754</v>
+        <v>-0.3205</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1152</v>
+        <v>0.0531</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0398</v>
+        <v>-0.3736</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5058</v>
+        <v>-0.3268</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5058</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9423</v>
+        <v>-5.495</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.449</v>
+        <v>-3.2675</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4933</v>
+        <v>-2.2276</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2869</v>
+        <v>-6.1519</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1169</v>
+        <v>-1.4563</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.17</v>
+        <v>-4.6956</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.227</v>
+        <v>-3.7732</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3552</v>
+        <v>-0.8381</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.8718</v>
+        <v>-2.9351</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0599</v>
+        <v>-2.3786</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7617</v>
+        <v>-0.6182</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2982</v>
+        <v>-1.7604</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2276</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.6829</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4553</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1009</v>
+        <v>0.4504</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5391</v>
+        <v>0.348</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5618</v>
+        <v>0.1024</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3268</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3268</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3783</v>
+        <v>-6.1658</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6201</v>
+        <v>-3.5016</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7583</v>
+        <v>-2.6642</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4591</v>
@@ -1468,13 +1468,13 @@
         <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8478</v>
+        <v>-0.6352</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4694</v>
+        <v>-0.351</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3784</v>
+        <v>-0.2843</v>
       </c>
       <c r="V13" t="n">
         <v>-2.7951</v>
@@ -1504,10 +1504,10 @@
         <v>-15.6091</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1616</v>
+        <v>10.1617</v>
       </c>
       <c r="F14" t="n">
-        <v>-25.7708</v>
+        <v>-25.771</v>
       </c>
       <c r="G14" t="n">
         <v>-4.1383</v>
@@ -1531,7 +1531,7 @@
         <v>-22.337</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.622999999999999</v>
+        <v>-8.623000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>-13.7141</v>
@@ -1543,19 +1543,19 @@
         <v>-13.658</v>
       </c>
       <c r="R14" t="n">
-        <v>7.9672</v>
+        <v>7.967200000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4411999999999999</v>
+        <v>0.4412</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0188</v>
+        <v>1.0185</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5776000000000001</v>
+        <v>-0.5775000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.2213</v>
+        <v>-6.221299999999999</v>
       </c>
       <c r="W14" t="n">
         <v>4.602</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7444</v>
+        <v>9.3658</v>
       </c>
       <c r="E15" t="n">
-        <v>9.150399999999999</v>
+        <v>8.0844</v>
       </c>
       <c r="F15" t="n">
-        <v>1.594</v>
+        <v>1.2814</v>
       </c>
       <c r="G15" t="n">
         <v>2.587</v>
@@ -1624,13 +1624,13 @@
         <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1347</v>
+        <v>0.7561</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2722</v>
+        <v>0.2062</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8625</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>4.4293</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.1241</v>
+        <v>7.0278</v>
       </c>
       <c r="E16" t="n">
-        <v>8.173500000000001</v>
+        <v>7.1075</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0494</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>5.7088</v>
@@ -1702,13 +1702,13 @@
         <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8023</v>
+        <v>0.706</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4813</v>
+        <v>0.4153</v>
       </c>
       <c r="U16" t="n">
-        <v>0.321</v>
+        <v>0.2908</v>
       </c>
       <c r="V16" t="n">
         <v>0.1578</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4557</v>
+        <v>2.7147</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5445</v>
+        <v>3.4261</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0889</v>
+        <v>-0.7114</v>
       </c>
       <c r="G17" t="n">
         <v>3.1302</v>
@@ -1780,13 +1780,13 @@
         <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.151</v>
+        <v>0.1081</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1111</v>
+        <v>-0.0073</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2621</v>
+        <v>0.1154</v>
       </c>
       <c r="V17" t="n">
         <v>0.387</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0751</v>
+        <v>2.0194</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4992</v>
+        <v>3.973</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4241</v>
+        <v>-1.9536</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1073</v>
@@ -1858,13 +1858,13 @@
         <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4518</v>
+        <v>-0.5075</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9758</v>
+        <v>-0.5021</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.476</v>
+        <v>-0.0055</v>
       </c>
       <c r="V18" t="n">
         <v>2.1789</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7217</v>
+        <v>1.8829</v>
       </c>
       <c r="E19" t="n">
-        <v>1.386</v>
+        <v>2.452</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6643</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0.4916</v>
@@ -1936,13 +1936,13 @@
         <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9567</v>
+        <v>0.2045</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5391</v>
+        <v>0.5269</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4176</v>
+        <v>-0.3224</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0895</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0655</v>
+        <v>0.1533</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3314</v>
+        <v>0.244</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2659</v>
+        <v>-0.0907</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8355</v>
+        <v>0.1218</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7929</v>
+        <v>0.8819</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0426</v>
+        <v>-0.7601</v>
       </c>
       <c r="J20" t="n">
-        <v>1.36</v>
+        <v>0.4357</v>
       </c>
       <c r="K20" t="n">
-        <v>1.003</v>
+        <v>0.8683</v>
       </c>
       <c r="L20" t="n">
-        <v>0.357</v>
+        <v>-0.4326</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1956</v>
+        <v>-0.3139</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7959</v>
+        <v>0.0135</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3997</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3658</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2276</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5934</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1673</v>
+        <v>-0.2856</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1165</v>
+        <v>0.4016</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0508</v>
+        <v>-0.6873</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7025</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3155</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>0.387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. LOPEZ</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2421</v>
+        <v>0.1282</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0697</v>
+        <v>1.3314</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1724</v>
+        <v>-1.2032</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1724</v>
+        <v>-1.8355</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1724</v>
+        <v>-0.7929</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1.0426</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.003</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1724</v>
+        <v>-3.1956</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1724</v>
+        <v>-1.7959</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.3997</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0697</v>
+        <v>-0.1046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0697</v>
+        <v>-0.1165</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.0119</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>X. LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8478</v>
+        <v>-0.2421</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3483</v>
+        <v>-0.0697</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4996</v>
+        <v>-0.1724</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1218</v>
+        <v>-0.1724</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8819</v>
+        <v>-0.1724</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7601</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4357</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8683</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4326</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3139</v>
+        <v>-0.1724</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0135</v>
+        <v>-0.1724</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3275</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2276</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9105</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2867</v>
+        <v>-0.0697</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1906</v>
+        <v>-0.0697</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0961</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3729</v>
+        <v>-4.5367</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.283</v>
+        <v>-1.1646</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0899</v>
+        <v>-3.3722</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2488</v>
@@ -2404,13 +2404,13 @@
         <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0347</v>
+        <v>-0.1985</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4182</v>
+        <v>-0.2998</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3836</v>
+        <v>0.1013</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6342</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>15.6092</v>
+        <v>16.3988</v>
       </c>
       <c r="E26" t="n">
-        <v>25.7709</v>
+        <v>25.771</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.1619</v>
+        <v>-9.372299999999999</v>
       </c>
       <c r="G26" t="n">
         <v>4.138299999999999</v>
@@ -2482,13 +2482,13 @@
         <v>13.6579</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4412000000000003</v>
+        <v>0.3484999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5775999999999998</v>
+        <v>0.5775000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0187</v>
+        <v>-0.2291</v>
       </c>
       <c r="V26" t="n">
         <v>6.2212</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104750_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104750_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.1871</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.5058</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-10.8232</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104750_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.6019</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
